--- a/plantillas/99.xlsx
+++ b/plantillas/99.xlsx
@@ -23,19 +23,19 @@
     <definedName name="MARCA_9">Listas!$L$2:$L$3</definedName>
     <definedName name="MARCA_10">Listas!$M$2:$M$2</definedName>
     <definedName name="MARCA_11">Listas!$N$2:$N$18</definedName>
-    <definedName name="MARCA_12">Listas!$O$2:$O$14</definedName>
+    <definedName name="MARCA_12">Listas!$O$2:$O$13</definedName>
     <definedName name="MARCA_13">Listas!$P$2:$P$3</definedName>
     <definedName name="MARCA_14">Listas!$Q$2:$Q$13</definedName>
     <definedName name="MARCA_15">Listas!$R$2:$R$6</definedName>
-    <definedName name="MARCA_16">Listas!$S$2:$S$7</definedName>
+    <definedName name="MARCA_16">Listas!$S$2:$S$6</definedName>
     <definedName name="MARCA_17">Listas!$T$2:$T$12</definedName>
     <definedName name="MARCA_18">Listas!$U$2:$U$6</definedName>
     <definedName name="MARCA_19">Listas!$V$2:$V$11</definedName>
     <definedName name="MARCA_20">Listas!$W$2:$W$14</definedName>
-    <definedName name="MARCA_21">Listas!$X$2:$X$13</definedName>
+    <definedName name="MARCA_21">Listas!$X$2:$X$14</definedName>
     <definedName name="MARCA_22">Listas!$Y$2:$Y$25</definedName>
     <definedName name="MARCA_23">Listas!$Z$2:$Z$7</definedName>
-    <definedName name="MARCA_24">Listas!$AA$2:$AA$42</definedName>
+    <definedName name="MARCA_24">Listas!$AA$2:$AA$43</definedName>
     <definedName name="MARCA_25">Listas!$AB$2:$AB$5</definedName>
     <definedName name="MARCA_26">Listas!$AC$2:$AC$6</definedName>
     <definedName name="MARCA_27">Listas!$AD$2:$AD$4</definedName>
@@ -8683,7 +8683,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>FANCY FEAST CAZUELA ATUN Y SALMON POUCH · 90038490000</t>
+          <t>FANCY FEAST CHUNCKY POLLO 3 OZ · 93509350000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>FANCY FEAST CHUNCKY POLLO 3 OZ · 93509350000</t>
+          <t>FANCY FEAST ESTOFADO CON TUNA POUCH 85G · 90038470000</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>FANCY FEAST ESTOFADO CON TUNA POUCH 85G · 90038470000</t>
+          <t>FANCY FEAST FILETES PEQ SALMON POUCH · 90038480000</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>FANCY FEAST FILETES PEQ SALMON POUCH · 90038480000</t>
+          <t>FANCY FEAST PESCADO BLANCO Y TUNA 3OZ US · 90038500000</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>FANCY FEAST PESCADO BLANCO Y TUNA 3OZ US · 90038500000</t>
+          <t>FANCY FEAST TRUCHA 3 OZ · 93509370000</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -9853,11 +9853,6 @@
           <t>PA LECHE DE CABRA EN POLVO 150GM · 93519340000</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>FANCY FEAST TRUCHA 3 OZ · 93509370000</t>
-        </is>
-      </c>
       <c r="T7" t="inlineStr">
         <is>
           <t>FELIX MEGAMIX ADULTO 1KG MX · 90038520000</t>
@@ -10543,7 +10538,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>PROTEINA DE HUEVO PARA AVES 5OZ · 90480080000</t>
+          <t>HIGGINS VITA SEED LORO 5LBS · 90416570000</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -10695,7 +10690,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>SNACK HIGGINS MINERAL GRIT 6 OZ · 93504530000</t>
+          <t>PROTEINA DE HUEVO PARA AVES 5OZ · 90480080000</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -10832,7 +10827,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>SNACK HIGGINS SOAK N SPROUT 3 OZ. · 93504540000</t>
+          <t>SNACK HIGGINS MINERAL GRIT 6 OZ · 93504530000</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -10942,14 +10937,14 @@
           <t>DOG CHOW CORDERO POUCH 100G MX · 90038290000</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>EP SNACK PUMPKIN HARVEST MANZANA 6OZ · 93500000505</t>
-        </is>
-      </c>
       <c r="W14" t="inlineStr">
         <is>
           <t>GM PERRO LOW FAT CNTROL PESO Y SENIOR 4 · 93500000149</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>SNACK HIGGINS SOAK N SPROUT 3 OZ. · 93504540000</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -11772,7 +11767,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>KT ALIMENTO TIMOTHY SELECT COBAYA 3 · 93518140000</t>
+          <t>KT ALIMENTO PARA KOI 3LB · 93500000266</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
@@ -11844,7 +11839,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>KT BARRA  D SEMILLA P/LORO MIEL 7OZ · 90402120000</t>
+          <t>KT ALIMENTO TIMOTHY SELECT COBAYA 3 · 93518140000</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
@@ -11911,7 +11906,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>KT BARRA D SEMILLA P CACATUA 8 OZ. · 90407600000</t>
+          <t>KT BARRA  D SEMILLA P/LORO MIEL 7OZ · 90402120000</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
@@ -11968,7 +11963,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>KT BARRA DE SEMILLA P CONEJO 6OZ. · 90406790000</t>
+          <t>KT BARRA D SEMILLA P CACATUA 8 OZ. · 90407600000</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
@@ -12025,7 +12020,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>KT BARRA DE SEMILLA P PERICO 7 OZ · 90406800000</t>
+          <t>KT BARRA DE SEMILLA P CONEJO 6OZ. · 90406790000</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
@@ -12077,7 +12072,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>KT EXACT  LORO LARGE RB  4 LB · 90407300000</t>
+          <t>KT BARRA DE SEMILLA P PERICO 7 OZ · 90406800000</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
@@ -12129,7 +12124,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>KT EXACT PARA PICHONES 5 LB · 90407340000</t>
+          <t>KT EXACT  LORO LARGE RB  4 LB · 90407300000</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
@@ -12181,7 +12176,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>KT EXACT PARA PICHONES 7.5 OZ · 90404920000</t>
+          <t>KT EXACT PARA PICHONES 5 LB · 90407340000</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
@@ -12233,7 +12228,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>KT FIESTA GUACAMAYA 4.5 LB · 90406690000</t>
+          <t>KT EXACT PARA PICHONES 7.5 OZ · 90404920000</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
@@ -12285,7 +12280,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>KT FIESTA MAXI LORO 4.5LB · 90402160000</t>
+          <t>KT FIESTA GUACAMAYA 4.5 LB · 90406690000</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
@@ -12337,7 +12332,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>KT FIESTA SNACK PAPAYA PEQ. ESP 2.5 · 93507160000</t>
+          <t>KT FIESTA MAXI LORO 4.5LB · 90402160000</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
@@ -12389,7 +12384,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>KT FIESTA SNACK YOGURT FRESA/BANANA · 93506900000</t>
+          <t>KT FIESTA SNACK PAPAYA PEQ. ESP 2.5 · 93507160000</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
@@ -12436,7 +12431,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>KT FIESTA TROCITOS DE PAPAYA 2.5OZ · 93506770000</t>
+          <t>KT FIESTA SNACK YOGURT FRESA/BANANA · 93506900000</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
@@ -12483,7 +12478,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>KT FORTI DIET HAMSTER/GERBIL 3LB · 90404990000</t>
+          <t>KT FIESTA TROCITOS DE PAPAYA 2.5OZ · 93506770000</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr">
@@ -12530,7 +12525,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>KT FORTI DIET LORO 5 LB · 90407230000</t>
+          <t>KT FORTI DIET HAMSTER/GERBIL 3LB · 90404990000</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
@@ -12577,7 +12572,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>KT FORTI DIET PERICO 2 LB · 90404800000</t>
+          <t>KT FORTI DIET LORO 5 LB · 90407230000</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
@@ -12619,7 +12614,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>KT FORTI DIET PERICOS 5 LBS · 90400000000</t>
+          <t>KT FORTI DIET PERICO 2 LB · 90404800000</t>
         </is>
       </c>
       <c r="AH39" t="inlineStr">
@@ -12661,7 +12656,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>KT SNACK FRESA P/ROEDORES 5.5OZ · 93517190000</t>
+          <t>KT FORTI DIET PERICOS 5 LBS · 90400000000</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
@@ -12693,7 +12688,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>KT SNACK NATURAL P/CONEJOS Y COBAYO · 93517210000</t>
+          <t>KT SNACK FRESA P/ROEDORES 5.5OZ · 93517190000</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
@@ -12725,7 +12720,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>KT SUPREME PALOMA 6/5LB · 93500800000</t>
+          <t>KT SNACK NATURAL P/CONEJOS Y COBAYO · 93517210000</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
@@ -12748,6 +12743,11 @@
       <c r="B43" t="inlineStr">
         <is>
           <t>MARCA_42</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>KT SUPREME PALOMA 6/5LB · 93500800000</t>
         </is>
       </c>
       <c r="AH43" t="inlineStr">
@@ -13152,7 +13152,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -13672,7 +13672,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -13912,7 +13912,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -14312,7 +14312,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15612,7 +15612,7 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -16712,7 +16712,7 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -16903,36 +16903,36 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>EP SNACK PUMPKIN HARVEST MANZANA 6OZ · 93500000505</t>
+          <t>ERA SYBARITE LATA CACHORROS 400G · 93519090000</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>93500000505</t>
+          <t>93519090000</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>EMERALD</t>
+          <t>ERA</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ERA SYBARITE LATA CACHORROS 400G · 93519090000</t>
+          <t>ERA SYBARITE LATAPOLLO/PESCADO 400G · 93519100000</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>93519090000</t>
+          <t>93519100000</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -16943,36 +16943,36 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ERA SYBARITE LATAPOLLO/PESCADO 400G · 93519100000</t>
+          <t>D PA LINATONE SUPLEMENTO ANTICAIDA 16 · 93519850000</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>93519100000</t>
+          <t>93519850000</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>ERA</t>
+          <t>ESBILAC</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>D PA LINATONE SUPLEMENTO ANTICAIDA 16 · 93519850000</t>
+          <t>ESBILAC LECHE EN POLVO 12 ONZ · 90311050000</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>93519850000</t>
+          <t>90311050000</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -16983,16 +16983,16 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ESBILAC LECHE EN POLVO 12 ONZ · 90311050000</t>
+          <t>ESBILAC PAPILLA P CACHORROS 14 OZ. · 90312680000</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>90311050000</t>
+          <t>90312680000</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -17003,16 +17003,16 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ESBILAC PAPILLA P CACHORROS 14 OZ. · 90312680000</t>
+          <t>KMR PAPILLA P GATITOS 2STEP 14 OZ. · 90404010000</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>90312680000</t>
+          <t>90404010000</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -17023,16 +17023,16 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>KMR PAPILLA P GATITOS 2STEP 14 OZ. · 90404010000</t>
+          <t>LECHE ESBILAC P GATOS 6 OZ. · 90401410000</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>90404010000</t>
+          <t>90401410000</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -17043,16 +17043,16 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>LECHE ESBILAC P GATOS 6 OZ. · 90401410000</t>
+          <t>PA LECHE DE CABRA EN POLVO 150GM · 93519340000</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>90401410000</t>
+          <t>93519340000</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -17063,16 +17063,16 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>PA LECHE DE CABRA EN POLVO 150GM · 93519340000</t>
+          <t>PA VITAM/MINERALES GEL P/GATO · 90330330000</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>93519340000</t>
+          <t>90330330000</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -17083,16 +17083,16 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>PA VITAM/MINERALES GEL P/GATO · 90330330000</t>
+          <t>PA VITAMINA EN GEL CALORIAS P/GATO · 90330310000</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>90330330000</t>
+          <t>90330310000</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -17103,16 +17103,16 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>PA VITAMINA EN GEL CALORIAS P/GATO · 90330310000</t>
+          <t>PA VITAMINA EN GEL CALORIAS P/PERRO · 90330290000</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>90330310000</t>
+          <t>90330290000</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -17123,16 +17123,16 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>PA VITAMINA EN GEL CALORIAS P/PERRO · 90330290000</t>
+          <t>PET LAC LECHE EN POLVO P/GATOS 10.5 · 93519350000</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>90330290000</t>
+          <t>93519350000</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -17143,16 +17143,16 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>PET LAC LECHE EN POLVO P/GATOS 10.5 · 93519350000</t>
+          <t>PETLAC LECHE EN POLVO P/PERROS 10.5 · 93519360000</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>93519350000</t>
+          <t>93519360000</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -17163,16 +17163,16 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>PETLAC LECHE EN POLVO P/PERROS 10.5 · 93519360000</t>
+          <t>SUPL EN POLVO LECHE DE CABRA 12OZ · 90308700000</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>93519360000</t>
+          <t>90308700000</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -17183,36 +17183,36 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SUPL EN POLVO LECHE DE CABRA 12OZ · 90308700000</t>
+          <t>EUK DOG LARGE PUPPY 3 Kg (6.61 lbs) · 90018520000</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>90308700000</t>
+          <t>90018520000</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>ESBILAC</t>
+          <t>EUKANUBA</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>EUK DOG LARGE PUPPY 3 Kg (6.61 lbs) · 90018520000</t>
+          <t>EUK DOG MEDIUM PUPPY  3 Kg (6.61 lbs) · 90018490000</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>90018520000</t>
+          <t>90018490000</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -17223,16 +17223,16 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>EUK DOG MEDIUM PUPPY  3 Kg (6.61 lbs) · 90018490000</t>
+          <t>EUK DOG MEDIUM SENIOR  3 Kg (6.61 lbs) · 90018630000</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>90018490000</t>
+          <t>90018630000</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -17243,16 +17243,16 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>EUK DOG MEDIUM SENIOR  3 Kg (6.61 lbs) · 90018630000</t>
+          <t>EUK DOG SMALL PUPPY 3 Kg (6.61 lbs) · 90018470000</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>90018630000</t>
+          <t>90018470000</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -17263,16 +17263,16 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>EUK DOG SMALL PUPPY 3 Kg (6.61 lbs) · 90018470000</t>
+          <t>EUK RZ PEQUENA CONTROL DE PESO 4LB · 93518600000</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>90018470000</t>
+          <t>93518600000</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -17283,36 +17283,36 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>EUK RZ PEQUENA CONTROL DE PESO 4LB · 93518600000</t>
+          <t>FANCY FEAST CHUNCKY POLLO 3 OZ · 93509350000</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>93518600000</t>
+          <t>93509350000</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>EUKANUBA</t>
+          <t>FANCY FEAST</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>FANCY FEAST CAZUELA ATUN Y SALMON POUCH · 90038490000</t>
+          <t>FANCY FEAST ESTOFADO CON TUNA POUCH 85G · 90038470000</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>90038490000</t>
+          <t>90038470000</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -17323,16 +17323,16 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>FANCY FEAST CHUNCKY POLLO 3 OZ · 93509350000</t>
+          <t>FANCY FEAST FILETES PEQ SALMON POUCH · 90038480000</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>93509350000</t>
+          <t>90038480000</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -17343,16 +17343,16 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>FANCY FEAST ESTOFADO CON TUNA POUCH 85G · 90038470000</t>
+          <t>FANCY FEAST PESCADO BLANCO Y TUNA 3OZ US · 90038500000</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>90038470000</t>
+          <t>90038500000</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -17363,16 +17363,16 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>FANCY FEAST FILETES PEQ SALMON POUCH · 90038480000</t>
+          <t>FANCY FEAST TRUCHA 3 OZ · 93509370000</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>90038480000</t>
+          <t>93509370000</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -17383,56 +17383,56 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>FANCY FEAST PESCADO BLANCO Y TUNA 3OZ US · 90038500000</t>
+          <t>FELIX CARNE 85G MX · 90038460000</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>90038500000</t>
+          <t>90038460000</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>FANCY FEAST</t>
+          <t>FELIX</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>FANCY FEAST TRUCHA 3 OZ · 93509370000</t>
+          <t>FELIX CARNE GATITOS 85G MX · 90038450000</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>93509370000</t>
+          <t>90038450000</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>FANCY FEAST</t>
+          <t>FELIX</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>FELIX CARNE 85G MX · 90038460000</t>
+          <t>FELIX DELICIAS DE LA GRANJA ADULTO 1KG M · 90038530000</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>90038460000</t>
+          <t>90038530000</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17443,16 +17443,16 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>FELIX CARNE GATITOS 85G MX · 90038450000</t>
+          <t>FELIX DELICIAS DEL MAR ADULTO 1KG MX · 90038540000</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>90038450000</t>
+          <t>90038540000</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17463,16 +17463,16 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>FELIX DELICIAS DE LA GRANJA ADULTO 1KG M · 90038530000</t>
+          <t>FELIX GATITOS 500G MX · 90038510000</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>90038530000</t>
+          <t>90038510000</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17483,16 +17483,16 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>FELIX DELICIAS DEL MAR ADULTO 1KG MX · 90038540000</t>
+          <t>FELIX MEGAMIX ADULTO 1KG MX · 90038520000</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>90038540000</t>
+          <t>90038520000</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17503,16 +17503,16 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>FELIX GATITOS 500G MX · 90038510000</t>
+          <t>FELIX MEGAMIX ADULTO 500G MX · 90038550000</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>90038510000</t>
+          <t>90038550000</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17523,16 +17523,16 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>FELIX MEGAMIX ADULTO 1KG MX · 90038520000</t>
+          <t>FELIX PATE PAVO Y MENUDENCIAS 156G · 93502660000</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>90038520000</t>
+          <t>93502660000</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17543,16 +17543,16 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>FELIX MEGAMIX ADULTO 500G MX · 90038550000</t>
+          <t>FELIX PATE PESCADO Y ATUN 156G · 93502640000</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>90038550000</t>
+          <t>93502640000</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17563,16 +17563,16 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>FELIX PATE PAVO Y MENUDENCIAS 156G · 93502660000</t>
+          <t>FELIX PATE SALMON 156G · 93502650000</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>93502660000</t>
+          <t>93502650000</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17583,16 +17583,16 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>FELIX PATE PESCADO Y ATUN 156G · 93502640000</t>
+          <t>FELIX POLLO 85G MX · 90038440000</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>93502640000</t>
+          <t>90038440000</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17603,56 +17603,56 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>FELIX PATE SALMON 156G · 93502650000</t>
+          <t>SEM ALPISTE  1 LB · 90426180000</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>93502650000</t>
+          <t>90426180000</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>GENÉRICO (reempaque)</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>FELIX POLLO 85G MX · 90038440000</t>
+          <t>SEMILLA DE GIRASOL 2 LB · 90402150000</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>90038440000</t>
+          <t>90402150000</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>GENÉRICO (reempaque)</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>SEM ALPISTE  1 LB · 90426180000</t>
+          <t>SEMILLAS DE GIRASOL JUMBO 454GR · 90426190000</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>90426180000</t>
+          <t>90426190000</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17663,16 +17663,16 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>SEMILLA DE GIRASOL 2 LB · 90402150000</t>
+          <t>SEMILLAS DE GIRASOL JUMBO 5 LB · 90426200000</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>90402150000</t>
+          <t>90426200000</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17683,16 +17683,16 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>SEMILLAS DE GIRASOL JUMBO 454GR · 90426190000</t>
+          <t>SEMILLAS DE MIJO VARIADAS 1LB · 93500750000</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>90426190000</t>
+          <t>93500750000</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17703,56 +17703,56 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>SEMILLAS DE GIRASOL JUMBO 5 LB · 90426200000</t>
+          <t>D 3 BEARS ALIMENTO LIOFILIZA PESCADO 1LB · 93500000210</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>90426200000</t>
+          <t>93500000210</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>GENÉRICO (reempaque)</t>
+          <t>GRANDMA LUCY'S</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>SEMILLAS DE MIJO VARIADAS 1LB · 93500750000</t>
+          <t>D 3 BEARS ALIMENTO LIOFILIZA PESCADO 3LB · 93500000211</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>93500750000</t>
+          <t>93500000211</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>GENÉRICO (reempaque)</t>
+          <t>GRANDMA LUCY'S</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>D 3 BEARS ALIMENTO LIOFILIZA PESCADO 1LB · 93500000210</t>
+          <t>D 3 BEARS ALIMENTO LIOFILIZA PESCADO MUE · 90000510000</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>93500000210</t>
+          <t>90000510000</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17763,16 +17763,16 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>D 3 BEARS ALIMENTO LIOFILIZA PESCADO 3LB · 93500000211</t>
+          <t>D 3 BEARS ALIMENTO LIOFILIZADO CARNE 1LB · 93500000208</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>93500000211</t>
+          <t>93500000208</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17783,16 +17783,16 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>D 3 BEARS ALIMENTO LIOFILIZA PESCADO MUE · 90000510000</t>
+          <t>D 3 BEARS ALIMENTO LIOFILIZADO CARNE MUE · 90000500000</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>90000510000</t>
+          <t>90000500000</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17803,16 +17803,16 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>D 3 BEARS ALIMENTO LIOFILIZADO CARNE 1LB · 93500000208</t>
+          <t>D 3 BEARS ALIMENTO LIOFILIZADO POLLO MUE · 90000490000</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>93500000208</t>
+          <t>90000490000</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17823,16 +17823,16 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>D 3 BEARS ALIMENTO LIOFILIZADO CARNE MUE · 90000500000</t>
+          <t>D GL SUPLEMENTO DIGESTIVO 6OZ · 93500000212</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>90000500000</t>
+          <t>93500000212</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17843,16 +17843,16 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>D 3 BEARS ALIMENTO LIOFILIZADO POLLO MUE · 90000490000</t>
+          <t>D GL SUPLEMENTO INFLAMACION 6OZ · 93500000213</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>90000490000</t>
+          <t>93500000213</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17863,16 +17863,16 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>D GL SUPLEMENTO DIGESTIVO 6OZ · 93500000212</t>
+          <t>D GL SUPLEMENTO PARA VEJIGA 6OZ · 93500000214</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>93500000212</t>
+          <t>93500000214</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17883,16 +17883,16 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>D GL SUPLEMENTO INFLAMACION 6OZ · 93500000213</t>
+          <t>D GL SUPLEMENTO PIEL Y PELAJE 6OZ · 93500000215</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>93500000213</t>
+          <t>93500000215</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17903,56 +17903,56 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>D GL SUPLEMENTO PARA VEJIGA 6OZ · 93500000214</t>
+          <t>D GM COUNT NAT ESTOMAG SENSIB/ PERRO 24 · 93500000144</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>93500000214</t>
+          <t>93500000144</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>GRANDMA LUCY'S</t>
+          <t>GRANDMA MAE'S</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>D GL SUPLEMENTO PIEL Y PELAJE 6OZ · 93500000215</t>
+          <t>D GM GF PERRO LG COUNT NATURALS PAVO 14L · 93500000123</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>93500000215</t>
+          <t>93500000123</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>GRANDMA LUCY'S</t>
+          <t>GRANDMA MAE'S</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>D GM COUNT NAT ESTOMAG SENSIB/ PERRO 24 · 93500000144</t>
+          <t>D GM PERRO COUNT NATURAL MEZCLA LA GR 14 · 93500000156</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>93500000144</t>
+          <t>93500000156</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17963,12 +17963,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>D GM GF PERRO LG COUNT NATURALS PAVO 14L · 93500000123</t>
+          <t>GM COUNT NAT CORDERO/ PESCADO P PERROS 4 · 93500000134</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>93500000123</t>
+          <t>93500000134</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -17983,16 +17983,16 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>D GM PERRO COUNT NATURAL MEZCLA LA GR 14 · 93500000156</t>
+          <t>GM COUNT NAT ESTOMAG SENSIBL/ PERRO 12 · 93500000143</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>93500000156</t>
+          <t>93500000143</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18003,16 +18003,16 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>GM COUNT NAT CORDERO/ PESCADO P PERROS 4 · 93500000134</t>
+          <t>GM COUNT NAT ESTOMAG SENSIBLE/ PERRO 4LB · 93500000142</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>93500000134</t>
+          <t>93500000142</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18023,16 +18023,16 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>GM COUNT NAT ESTOMAG SENSIBL/ PERRO 12 · 93500000143</t>
+          <t>GM COUNT NAT PERROS CACHORROS 4LB · 93500000146</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>93500000143</t>
+          <t>93500000146</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18043,16 +18043,16 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>GM COUNT NAT ESTOMAG SENSIBLE/ PERRO 4LB · 93500000142</t>
+          <t>GM COUNT NAT SALMON/ PESCADO P PERROS 12 · 93500000139</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>93500000142</t>
+          <t>93500000139</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18063,16 +18063,16 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>GM COUNT NAT PERROS CACHORROS 4LB · 93500000146</t>
+          <t>GM GF GATOS COUNTRY NATURALS POLLO 3LB · 93500000159</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>93500000146</t>
+          <t>93500000159</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18083,16 +18083,16 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>GM COUNT NAT SALMON/ PESCADO P PERROS 12 · 93500000139</t>
+          <t>GM GF PERRO COUNT NATURAL MULTI PROT 4LB · 93500000130</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>93500000139</t>
+          <t>93500000130</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18103,16 +18103,16 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>GM GF GATOS COUNTRY NATURALS POLLO 3LB · 93500000159</t>
+          <t>GM GF PERRO COUNTRY NATURALS PAVO 4LB · 93500000109</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>93500000159</t>
+          <t>93500000109</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18123,16 +18123,16 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>GM GF PERRO COUNT NATURAL MULTI PROT 4LB · 93500000130</t>
+          <t>GM GF PERRO COUNTRY NATURALS POLLO 4LB · 93500000102</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>93500000130</t>
+          <t>93500000102</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18143,16 +18143,16 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>GM GF PERRO COUNTRY NATURALS PAVO 4LB · 93500000109</t>
+          <t>GM PERRO LOW FAT CNTROL PESO Y SENIOR 4 · 93500000149</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>93500000109</t>
+          <t>93500000149</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18163,56 +18163,56 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>GM GF PERRO COUNTRY NATURALS POLLO 4LB · 93500000102</t>
+          <t>HIGGINS ALIM CONURO Y PERIQ 2.5LB · 93510560000</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>93500000102</t>
+          <t>93510560000</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>GRANDMA MAE'S</t>
+          <t>HIGGINS</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>GM PERRO LOW FAT CNTROL PESO Y SENIOR 4 · 93500000149</t>
+          <t>HIGGINS SNACK BOCADOS DE MIJO 1OZ · 93510480000</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>93500000149</t>
+          <t>93510480000</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>GRANDMA MAE'S</t>
+          <t>HIGGINS</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>HIGGINS ALIM CONURO Y PERIQ 2.5LB · 93510560000</t>
+          <t>HIGGINS SNACK FRUTAS VEGETALES 5OZ · 93510450000</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>93510560000</t>
+          <t>93510450000</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18223,16 +18223,16 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>HIGGINS SNACK BOCADOS DE MIJO 1OZ · 93510480000</t>
+          <t>HIGGINS SUNBURST ALIM COBAYOS 3LB · 93510430000</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>93510480000</t>
+          <t>93510430000</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18243,16 +18243,16 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>HIGGINS SNACK FRUTAS VEGETALES 5OZ · 93510450000</t>
+          <t>HIGGINS SUNBURST ALIM P CONEJOS 3LB · 93510440000</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>93510450000</t>
+          <t>93510440000</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18263,16 +18263,16 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>HIGGINS SUNBURST ALIM COBAYOS 3LB · 93510430000</t>
+          <t>HIGGINS SUNBURST ALIM/HAMSTERS 2.5 · 93518320000</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>93510430000</t>
+          <t>93518320000</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18283,16 +18283,16 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>HIGGINS SUNBURST ALIM P CONEJOS 3LB · 93510440000</t>
+          <t>HIGGINS VITA LORO 3LBS · 90739860000</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>93510440000</t>
+          <t>90739860000</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18303,16 +18303,16 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>HIGGINS SUNBURST ALIM/HAMSTERS 2.5 · 93518320000</t>
+          <t>HIGGINS VITA SEED CACATUA 2.5 · 90416550000</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>93518320000</t>
+          <t>90416550000</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18323,12 +18323,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>HIGGINS VITA LORO 3LBS · 90739860000</t>
+          <t>HIGGINS VITA SEED FINCHE 2LBS · 90416530000</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>90739860000</t>
+          <t>90416530000</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -18343,12 +18343,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>HIGGINS VITA SEED CACATUA 2.5 · 90416550000</t>
+          <t>HIGGINS VITA SEED LORO 5LBS · 90416570000</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>90416550000</t>
+          <t>90416570000</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -18363,16 +18363,16 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>HIGGINS VITA SEED FINCHE 2LBS · 90416530000</t>
+          <t>PROTEINA DE HUEVO PARA AVES 5OZ · 90480080000</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>90416530000</t>
+          <t>90480080000</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18383,16 +18383,16 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>PROTEINA DE HUEVO PARA AVES 5OZ · 90480080000</t>
+          <t>SNACK HIGGINS MINERAL GRIT 6 OZ · 93504530000</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>90480080000</t>
+          <t>93504530000</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18403,12 +18403,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>SNACK HIGGINS MINERAL GRIT 6 OZ · 93504530000</t>
+          <t>SNACK HIGGINS SOAK N SPROUT 3 OZ. · 93504540000</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>93504530000</t>
+          <t>93504540000</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -18423,36 +18423,36 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>SNACK HIGGINS SOAK N SPROUT 3 OZ. · 93504540000</t>
+          <t>SD ADULT 7+ ACT LONG FELINO 4LB · 93506550000</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>93504540000</t>
+          <t>93506550000</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>HIGGINS</t>
+          <t>HILL'S</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>SD ADULT 7+ ACT LONG FELINO 4LB · 93506550000</t>
+          <t>SD ADULT AF SM CORDERO/ARROZ 4.5L · 93506430000</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>93506550000</t>
+          <t>93506430000</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18463,16 +18463,16 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>SD ADULT AF SM CORDERO/ARROZ 4.5L · 93506430000</t>
+          <t>SD ADULTO 1-6  6.6lb · 93509800001</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>93506430000</t>
+          <t>93509800001</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18483,16 +18483,16 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>SD ADULTO 1-6  6.6lb · 93509800001</t>
+          <t>SD ADULTO 1-6 BOCADOS PQNOS 4,4 LB · 93509790001</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>93509800001</t>
+          <t>93509790001</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18503,16 +18503,16 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>SD ADULTO 1-6 BOCADOS PQNOS 4,4 LB · 93509790001</t>
+          <t>SD ADULTO 7+ BOCADOS PQNOS  4.4 LB · 93506470001</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>93509790001</t>
+          <t>93506470001</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18523,16 +18523,16 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>SD ADULTO 7+ BOCADOS PQNOS  4.4 LB · 93506470001</t>
+          <t>SD ADULTO 7+6.6lb · 93506480001</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>93506470001</t>
+          <t>93506480001</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18543,16 +18543,16 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>SD ADULTO 7+6.6lb · 93506480001</t>
+          <t>SD ADULTO ESTOMAGO /PIEL SENS 15.5LB · 93507530001</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>93506480001</t>
+          <t>93507530001</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18563,16 +18563,16 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>SD ADULTO ESTOMAGO /PIEL SENS 15.5LB · 93507530001</t>
+          <t>SD ADULTO ESTOMAGO/PIEL SENSIBLE 4LB · 93507510001</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>93507530001</t>
+          <t>93507510001</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18583,16 +18583,16 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>SD ADULTO ESTOMAGO/PIEL SENSIBLE 4LB · 93507510001</t>
+          <t>SD ADULTO INDOOR FELINO 3.5LB · 93506540000</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>93507510001</t>
+          <t>93506540000</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18603,16 +18603,16 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>SD ADULTO INDOOR FELINO 3.5LB · 93506540000</t>
+          <t>SD ADULTO LIGHT FELINO 4LB · 93506530000</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>93506540000</t>
+          <t>93506530000</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18623,16 +18623,16 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>SD ADULTO LIGHT FELINO 4LB · 93506530000</t>
+          <t>SD ADULTO RAZAS PEQUEÑAS Y TOY 4.5 · 93515520000</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>93506530000</t>
+          <t>93515520000</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18643,16 +18643,16 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>SD ADULTO RAZAS PEQUEÑAS Y TOY 4.5 · 93515520000</t>
+          <t>SD ADULTO SENSIBLE MINI 4LB · 93516920000</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>93515520000</t>
+          <t>93516920000</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18663,16 +18663,16 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>SD ADULTO SENSIBLE MINI 4LB · 93516920000</t>
+          <t>SD ADULTO SMALL Y TOY LIGHT 4.5 · 93516910000</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>93516920000</t>
+          <t>93516910000</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18683,16 +18683,16 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>SD ADULTO SMALL Y TOY LIGHT 4.5 · 93516910000</t>
+          <t>SD ALIMENTO PARA PERRO ADULTO 15LB · 93515020000</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>93516910000</t>
+          <t>93515020000</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18703,16 +18703,16 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>SD ALIMENTO PARA PERRO ADULTO 15LB · 93515020000</t>
+          <t>SD CACHORRO DESARROLLO 4.5LB · 93509780000</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>93515020000</t>
+          <t>93509780000</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18723,16 +18723,16 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>SD CACHORRO DESARROLLO 4.5LB · 93509780000</t>
+          <t>SD CACHORROS RAZAS PQNAS Y TOY 4.5 · 93515510000</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>93509780000</t>
+          <t>93515510000</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18743,12 +18743,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>SD CACHORROS RAZAS PQNAS Y TOY 4.5 · 93515510000</t>
+          <t>SD CANINE CACHORROS 15.5LB · 90304140000</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>93515510000</t>
+          <t>90304140000</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -18763,16 +18763,16 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>SD CANINE CACHORROS 15.5LB · 90304140000</t>
+          <t>SD FELINE ADULTO 4 LB · 90300090000</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>90304140000</t>
+          <t>90300090000</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18783,16 +18783,16 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>SD FELINE ADULTO 4 LB · 90300090000</t>
+          <t>SD FELINE GATITO 3.5LB · 90303640000</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>90300090000</t>
+          <t>90303640000</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18803,16 +18803,16 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>SD FELINE GATITO 3.5LB · 90303640000</t>
+          <t>SD GATITO INDOOR 3.5LB · 93516930000</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>90303640000</t>
+          <t>93516930000</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18823,16 +18823,16 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>SD GATITO INDOOR 3.5LB · 93516930000</t>
+          <t>SD GATO ADULT CTRL BOLAS/PELO 3.5 · 93509830000</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>93516930000</t>
+          <t>93509830000</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18843,12 +18843,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>SD GATO ADULT CTRL BOLAS/PELO 3.5 · 93509830000</t>
+          <t>SD GATO ADULTO SENSIBLE 3.5LB · 93516940000</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>93509830000</t>
+          <t>93516940000</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -18863,16 +18863,16 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>SD GATO ADULTO SENSIBLE 3.5LB · 93516940000</t>
+          <t>SD LATA ADULTO POLLO 13OZ · 93509850000</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>93516940000</t>
+          <t>93509850000</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18883,16 +18883,16 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>SD LATA ADULTO POLLO 13OZ · 93509850000</t>
+          <t>SD LATA CACHORRO POLLO 13OZ · 93509840000</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>93509850000</t>
+          <t>93509840000</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18903,36 +18903,36 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>SD LATA CACHORRO POLLO 13OZ · 93509840000</t>
+          <t>D HIMALAYAN SNACK MASTICABLE MANI LG · 93518010000</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>93509840000</t>
+          <t>93518010000</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>HILL'S</t>
+          <t>HIMALAYAN</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>D HIMALAYAN SNACK MASTICABLE MANI LG · 93518010000</t>
+          <t>D HIMALAYAN SNACK MASTICABLE MANI MD · 93518030000</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>93518010000</t>
+          <t>93518030000</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18943,16 +18943,16 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>D HIMALAYAN SNACK MASTICABLE MANI MD · 93518030000</t>
+          <t>D HIMALAYAN SNACK MASTICABLE MANI SM · 93518050000</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>93518030000</t>
+          <t>93518050000</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18963,16 +18963,16 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>D HIMALAYAN SNACK MASTICABLE MANI SM · 93518050000</t>
+          <t>D HIMALAYAN SNACK MASTICABLE POLLO LG · 93518000000</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>93518050000</t>
+          <t>93518000000</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18983,16 +18983,16 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>D HIMALAYAN SNACK MASTICABLE POLLO LG · 93518000000</t>
+          <t>D HIMALAYAN SNACK MASTICABLE POLLO MD · 93518020000</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>93518000000</t>
+          <t>93518020000</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19003,16 +19003,16 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>D HIMALAYAN SNACK MASTICABLE POLLO MD · 93518020000</t>
+          <t>D HIMALAYAN SNACK MASTICABLE POLLO SM · 93518040000</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>93518020000</t>
+          <t>93518040000</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19023,36 +19023,36 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>D HIMALAYAN SNACK MASTICABLE POLLO SM · 93518040000</t>
+          <t>D KT ALIMENTO PARA KOI 25LB · 93500000264</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>93518040000</t>
+          <t>93500000264</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>HIMALAYAN</t>
+          <t>KAYTEE</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>D KT ALIMENTO PARA KOI 25LB · 93500000264</t>
+          <t>D KT CUBOS DE TIMOTHY 1LB · 93507290000</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>93500000264</t>
+          <t>93507290000</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19063,16 +19063,16 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>D KT CUBOS DE TIMOTHY 1LB · 93507290000</t>
+          <t>D KT FDPH ALIM PARA PERIQUITOS 2LB · 93511590000</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>93507290000</t>
+          <t>93511590000</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19083,16 +19083,16 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>D KT FDPH ALIM PARA PERIQUITOS 2LB · 93511590000</t>
+          <t>D KT FDPH ALIM PARA PERIQUITOS 4LB · 93511600000</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>93511590000</t>
+          <t>93511600000</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19103,16 +19103,16 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>D KT FDPH ALIM PARA PERIQUITOS 4LB · 93511600000</t>
+          <t>KT ALIM EXACT LORO Y CONURO RB 4 LB · 90407280000</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>93511600000</t>
+          <t>90407280000</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19123,16 +19123,16 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>KT ALIM EXACT LORO Y CONURO RB 4 LB · 90407280000</t>
+          <t>KT ALIM FIESTA P PERIQUITO 2 LB · 90404720000</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>90407280000</t>
+          <t>90404720000</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19143,16 +19143,16 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>KT ALIM FIESTA P PERIQUITO 2 LB · 90404720000</t>
+          <t>KT ALIM KAYTEE FIESTA CONURO 4.5 LB · 90406700000</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>90404720000</t>
+          <t>90406700000</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19163,16 +19163,16 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>KT ALIM KAYTEE FIESTA CONURO 4.5 LB · 90406700000</t>
+          <t>KT ALIM TIMOTHY COMP P/CONEJOS 4.5 · 93507020000</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>90406700000</t>
+          <t>93507020000</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19183,16 +19183,16 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>KT ALIM TIMOTHY COMP P/CONEJOS 4.5 · 93507020000</t>
+          <t>KT ALIM TIMOTHY SELECT CONEJOS 3.5 · 93518150000</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>93507020000</t>
+          <t>93518150000</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19203,16 +19203,16 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>KT ALIM TIMOTHY SELECT CONEJOS 3.5 · 93518150000</t>
+          <t>KT ALIM. EXACT P PICHONES 18OZ. · 90404930000</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>93518150000</t>
+          <t>90404930000</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19223,16 +19223,16 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>KT ALIM. EXACT P PICHONES 18OZ. · 90404930000</t>
+          <t>KT ALIM. EXACT PERIQUITO RB 2 LB · 90405940000</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>90404930000</t>
+          <t>90405940000</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19243,16 +19243,16 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>KT ALIM. EXACT PERIQUITO RB 2 LB · 90405940000</t>
+          <t>KT ALIM. FIESTA MAX COBAYO 2.5 LB · 90407380000</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>90405940000</t>
+          <t>90407380000</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19263,12 +19263,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>KT ALIM. FIESTA MAX COBAYO 2.5 LB · 90407380000</t>
+          <t>KT ALIM. FIESTA MAX CONEJO 3.5LB · 90402840000</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>90407380000</t>
+          <t>90402840000</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -19283,16 +19283,16 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>KT ALIM. FIESTA MAX CONEJO 3.5LB · 90402840000</t>
+          <t>KT ALIM. FORTI DIET COBAYO 5 LB · 90407730000</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>90402840000</t>
+          <t>90407730000</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19303,16 +19303,16 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>KT ALIM. FORTI DIET COBAYO 5 LB · 90407730000</t>
+          <t>KT ALIM. FORTI DIET CONEJO 10 LB · 90407390000</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>90407730000</t>
+          <t>90407390000</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19323,16 +19323,16 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>KT ALIM. FORTI DIET CONEJO 10 LB · 90407390000</t>
+          <t>KT ALIM. FORTI DIET CONEJO 5 LB · 90405030000</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>90407390000</t>
+          <t>90405030000</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19343,16 +19343,16 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>KT ALIM. FORTI DIET CONEJO 5 LB · 90405030000</t>
+          <t>KT ALIM. SUPREME COBAYO 5 LB · 90405110000</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>90405030000</t>
+          <t>90405110000</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19363,16 +19363,16 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>KT ALIM. SUPREME COBAYO 5 LB · 90405110000</t>
+          <t>KT ALIM. SUPREME CONEJO 10LB · 90407440000</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>90405110000</t>
+          <t>90407440000</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19383,16 +19383,16 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>KT ALIM. SUPREME CONEJO 10LB · 90407440000</t>
+          <t>KT ALIM. SUPREME CONEJO 5 LB · 90405210000</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>90407440000</t>
+          <t>90405210000</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19403,16 +19403,16 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>KT ALIM. SUPREME CONEJO 5 LB · 90405210000</t>
+          <t>KT ALIM. SUPREME PERIQUITO 5 LB · 90404880000</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>90405210000</t>
+          <t>90404880000</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19423,16 +19423,16 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>KT ALIM. SUPREME PERIQUITO 5 LB · 90404880000</t>
+          <t>KT ALIMENTO PARA KOI 10LB · 93500000265</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>90404880000</t>
+          <t>93500000265</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19443,16 +19443,16 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>KT ALIMENTO PARA KOI 10LB · 93500000265</t>
+          <t>KT ALIMENTO PARA KOI 3LB · 93500000266</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>93500000265</t>
+          <t>93500000266</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         </is>
       </c>
       <c r="C353" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         </is>
       </c>
       <c r="C355" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -20252,7 +20252,7 @@
         </is>
       </c>
       <c r="C358" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -20272,7 +20272,7 @@
         </is>
       </c>
       <c r="C359" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         </is>
       </c>
       <c r="C362" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -20432,7 +20432,7 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         </is>
       </c>
       <c r="C369" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -20992,7 +20992,7 @@
         </is>
       </c>
       <c r="C395" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         </is>
       </c>
       <c r="C415" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -21652,7 +21652,7 @@
         </is>
       </c>
       <c r="C428" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -21672,7 +21672,7 @@
         </is>
       </c>
       <c r="C429" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         </is>
       </c>
       <c r="C438" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         </is>
       </c>
       <c r="C440" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         </is>
       </c>
       <c r="C442" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -22912,7 +22912,7 @@
         </is>
       </c>
       <c r="C491" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -23492,7 +23492,7 @@
         </is>
       </c>
       <c r="C520" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -23592,7 +23592,7 @@
         </is>
       </c>
       <c r="C525" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         </is>
       </c>
       <c r="C536" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -23912,7 +23912,7 @@
         </is>
       </c>
       <c r="C541" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -24052,7 +24052,7 @@
         </is>
       </c>
       <c r="C548" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -24172,7 +24172,7 @@
         </is>
       </c>
       <c r="C554" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -24232,7 +24232,7 @@
         </is>
       </c>
       <c r="C557" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -24412,7 +24412,7 @@
         </is>
       </c>
       <c r="C566" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
         </is>
       </c>
       <c r="C593" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -25012,7 +25012,7 @@
         </is>
       </c>
       <c r="C596" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -25072,7 +25072,7 @@
         </is>
       </c>
       <c r="C599" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -26032,7 +26032,7 @@
         </is>
       </c>
       <c r="C647" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
         </is>
       </c>
       <c r="C648" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -26412,7 +26412,7 @@
         </is>
       </c>
       <c r="C666" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         </is>
       </c>
       <c r="C673" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
         </is>
       </c>
       <c r="C681" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -26952,7 +26952,7 @@
         </is>
       </c>
       <c r="C693" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -27312,7 +27312,7 @@
         </is>
       </c>
       <c r="C711" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -27352,7 +27352,7 @@
         </is>
       </c>
       <c r="C713" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         </is>
       </c>
       <c r="C752" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -28392,7 +28392,7 @@
         </is>
       </c>
       <c r="C765" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -28450,7 +28450,7 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>19.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/99.xlsx
+++ b/plantillas/99.xlsx
@@ -13212,7 +13212,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -13392,7 +13392,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -14412,7 +14412,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17692,7 +17692,7 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19292,7 +19292,7 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         </is>
       </c>
       <c r="C326" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         </is>
       </c>
       <c r="C347" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20132,7 +20132,7 @@
         </is>
       </c>
       <c r="C352" t="n">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -20432,7 +20432,7 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -20532,7 +20532,7 @@
         </is>
       </c>
       <c r="C372" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         </is>
       </c>
       <c r="C387" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         </is>
       </c>
       <c r="C415" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -21412,7 +21412,7 @@
         </is>
       </c>
       <c r="C416" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         </is>
       </c>
       <c r="C422" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -21612,7 +21612,7 @@
         </is>
       </c>
       <c r="C426" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -21692,7 +21692,7 @@
         </is>
       </c>
       <c r="C430" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -21712,7 +21712,7 @@
         </is>
       </c>
       <c r="C431" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         </is>
       </c>
       <c r="C440" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -22352,7 +22352,7 @@
         </is>
       </c>
       <c r="C463" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         </is>
       </c>
       <c r="C467" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         </is>
       </c>
       <c r="C519" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -23492,7 +23492,7 @@
         </is>
       </c>
       <c r="C520" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         </is>
       </c>
       <c r="C536" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         </is>
       </c>
       <c r="C538" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -24112,7 +24112,7 @@
         </is>
       </c>
       <c r="C551" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -24132,7 +24132,7 @@
         </is>
       </c>
       <c r="C552" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -24292,7 +24292,7 @@
         </is>
       </c>
       <c r="C560" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         </is>
       </c>
       <c r="C577" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         </is>
       </c>
       <c r="C579" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -24812,7 +24812,7 @@
         </is>
       </c>
       <c r="C586" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         </is>
       </c>
       <c r="C587" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         </is>
       </c>
       <c r="C640" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -26032,7 +26032,7 @@
         </is>
       </c>
       <c r="C647" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -26312,7 +26312,7 @@
         </is>
       </c>
       <c r="C661" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -26412,7 +26412,7 @@
         </is>
       </c>
       <c r="C666" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         </is>
       </c>
       <c r="C667" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         </is>
       </c>
       <c r="C669" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -26852,7 +26852,7 @@
         </is>
       </c>
       <c r="C688" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         </is>
       </c>
       <c r="C716" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         </is>
       </c>
       <c r="C753" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -28450,7 +28450,7 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>21.10.2026</t>
         </is>
       </c>
     </row>
